--- a/samples/쿠팡_주문샘플.xlsx
+++ b/samples/쿠팡_주문샘플.xlsx
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>무농약 블루베리 1kg</t>
+          <t>여수 돌산갓 2kg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>냉동, 1kg</t>
+          <t>생갓</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>무농약 블루베리 1kg, 냉동, 1kg</t>
+          <t>여수 돌산갓 2kg, 생갓</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>국내산 햇사과 5kg</t>
+          <t>예산국수 중면 1.5kg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>중과(18~20과)</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>국내산 햇사과 5kg, 중과(18~20과)</t>
+          <t>예산국수 중면 1.5kg, 1개</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>제주 한라봉 3kg</t>
+          <t>국산 들기름 350ml</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>특품</t>
+          <t>1병</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>제주 한라봉 3kg, 특품</t>
+          <t>국산 들기름 350ml, 1병</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
